--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-01-18T20:00:37+00:00</t>
+    <t>2022-02-19T15:25:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-02-19T15:25:03+00:00</t>
+    <t>2022-05-23T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-05-23T06:59:28+00:00</t>
+    <t>2022-05-24T18:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-05-24T18:54:59+00:00</t>
+    <t>2022-08-17T21:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-17T21:15:17+00:00</t>
+    <t>2022-09-06T15:19:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T15:19:36+00:00</t>
+    <t>2022-09-06T18:47:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T18:47:55+00:00</t>
+    <t>2022-09-06T19:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T19:01:15+00:00</t>
+    <t>2022-09-06T19:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T19:02:52+00:00</t>
+    <t>2022-09-06T19:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T19:21:39+00:00</t>
+    <t>2022-09-13T07:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-13T07:22:16+00:00</t>
+    <t>2022-09-17T09:48:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-17T09:48:15+00:00</t>
+    <t>2022-09-17T09:59:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-17T09:59:31+00:00</t>
+    <t>2022-09-17T10:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-17T10:02:16+00:00</t>
+    <t>2022-10-04T11:09:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T11:09:51+00:00</t>
+    <t>2022-10-04T14:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T14:18:04+00:00</t>
+    <t>2022-10-04T19:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T19:52:49+00:00</t>
+    <t>2022-10-04T20:54:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T20:54:27+00:00</t>
+    <t>2022-10-11T09:25:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-11T09:25:49+00:00</t>
+    <t>2022-10-21T11:28:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-21T11:28:25+00:00</t>
+    <t>2022-10-21T11:53:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-21T11:53:19+00:00</t>
+    <t>2022-10-24T14:23:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="169">
   <si>
     <t>Property</t>
   </si>
@@ -43,6 +43,9 @@
     <t>Title</t>
   </si>
   <si>
+    <t>DK SOR Organization Type</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
@@ -52,10 +55,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-24T14:23:47+00:00</t>
+    <t>2022-10-24T22:55:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -691,82 +697,86 @@
       <c r="A5" t="s" s="2">
         <v>8</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" t="s" s="2">
+        <v>9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -785,434 +795,434 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1231,162 +1241,162 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-24T22:55:30+00:00</t>
+    <t>2022-11-07T08:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-07T08:18:22+00:00</t>
+    <t>2022-11-07T15:10:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-07T15:10:04+00:00</t>
+    <t>2022-11-08T22:20:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-08T22:20:55+00:00</t>
+    <t>2022-11-08T22:23:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-08T22:23:46+00:00</t>
+    <t>2022-11-30T21:48:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-30T21:48:52+00:00</t>
+    <t>2022-12-01T00:22:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-01T00:22:19+00:00</t>
+    <t>2022-12-01T21:15:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-01T21:15:09+00:00</t>
+    <t>2022-12-05T08:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:13:32+00:00</t>
+    <t>2022-12-05T08:52:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:52:10+00:00</t>
+    <t>2022-12-05T08:58:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:58:17+00:00</t>
+    <t>2022-12-05T09:15:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T09:15:32+00:00</t>
+    <t>2023-04-18T12:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-18T12:02:45+00:00</t>
+    <t>2023-04-24T21:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-24T21:40:58+00:00</t>
+    <t>2023-04-25T17:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-25T17:34:53+00:00</t>
+    <t>2023-04-30T20:59:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T20:59:20+00:00</t>
+    <t>2023-04-30T21:23:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T21:23:00+00:00</t>
+    <t>2023-05-05T00:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>3.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T00:02:52+00:00</t>
+    <t>2023-11-28T12:13:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -642,10 +642,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:13:03+00:00</t>
+    <t>2023-11-30T13:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T13:40:49+00:00</t>
+    <t>2023-11-30T14:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T14:55:40+00:00</t>
+    <t>2023-12-01T12:31:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-01T12:31:40+00:00</t>
+    <t>2023-12-01T13:42:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-01T13:42:49+00:00</t>
+    <t>2023-12-19T10:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:28:26+00:00</t>
+    <t>2023-12-19T10:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:34:37+00:00</t>
+    <t>2024-01-06T18:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-06T18:57:36+00:00</t>
+    <t>2024-01-08T22:02:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:06+00:00</t>
+    <t>2024-01-08T22:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:40+00:00</t>
+    <t>2024-03-19T10:43:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-19T10:43:29+00:00</t>
+    <t>2024-04-03T07:46:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:46:18+00:00</t>
+    <t>2024-04-03T10:16:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T10:16:02+00:00</t>
+    <t>2024-04-10T06:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -73,7 +73,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T06:34:41+00:00</t>
+    <t>2024-04-11T09:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-11T09:53:59+00:00</t>
+    <t>2024-04-12T06:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T06:23:14+00:00</t>
+    <t>2024-04-16T10:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-16T10:58:26+00:00</t>
+    <t>2024-04-18T15:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:20:26+00:00</t>
+    <t>2024-04-18T15:27:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:27:51+00:00</t>
+    <t>2024-04-22T11:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T11:01:11+00:00</t>
+    <t>2024-04-22T12:03:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T12:03:36+00:00</t>
+    <t>2024-04-22T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T13:38:01+00:00</t>
+    <t>2024-04-23T08:24:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T08:24:27+00:00</t>
+    <t>2024-04-23T10:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T10:50:14+00:00</t>
+    <t>2024-04-23T18:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T18:15:55+00:00</t>
+    <t>2024-05-02T12:47:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-02T12:47:39+00:00</t>
+    <t>2024-05-03T13:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T13:03:24+00:00</t>
+    <t>2024-05-06T06:35:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T06:35:09+00:00</t>
+    <t>2024-05-06T07:49:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T07:49:19+00:00</t>
+    <t>2024-05-06T14:14:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -7,8 +7,8 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from SNOMED CT" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from SNOMED CT 2" r:id="rId5" sheetId="3"/>
+    <sheet name="Include from SNOWMED CT" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from SNOWMED CT 2" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T14:14:33+00:00</t>
+    <t>2024-05-10T08:40:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T19:12:38+00:00</t>
+    <t>2024-05-12T08:40:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:40:34+00:00</t>
+    <t>2024-05-12T08:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include from SNOWMED CT" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from SNOWMED CT 2" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="169">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:41:58+00:00</t>
+    <t>2024-05-12T09:45:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,214 +109,418 @@
     <t>554221000005108</t>
   </si>
   <si>
+    <t>Dwilling place</t>
+  </si>
+  <si>
     <t>546821000005103</t>
   </si>
   <si>
+    <t>Occupational therapy clinic</t>
+  </si>
+  <si>
     <t>547011000005103</t>
   </si>
   <si>
+    <t>Physiotherapy clinic</t>
+  </si>
+  <si>
     <t>546811000005109</t>
   </si>
   <si>
+    <t>Rehabilitation center</t>
+  </si>
+  <si>
     <t>550621000005101</t>
   </si>
   <si>
+    <t>District nursing</t>
+  </si>
+  <si>
     <t>550631000005103</t>
   </si>
   <si>
+    <t>Midwife clinic</t>
+  </si>
+  <si>
     <t>550641000005106</t>
   </si>
   <si>
+    <t>Chiropractic clinic</t>
+  </si>
+  <si>
     <t>550651000005108</t>
   </si>
   <si>
+    <t>Medical laboratory</t>
+  </si>
+  <si>
     <t>550661000005105</t>
   </si>
   <si>
+    <t>Emergency medical service</t>
+  </si>
+  <si>
     <t>554211000005102</t>
   </si>
   <si>
+    <t>Prehospital unit</t>
+  </si>
+  <si>
     <t>550711000005101</t>
   </si>
   <si>
+    <t>Psychological counseling clinic</t>
+  </si>
+  <si>
     <t>550671000005100</t>
   </si>
   <si>
+    <t>Medical specialist practice site</t>
+  </si>
+  <si>
     <t>554061000005105</t>
   </si>
   <si>
+    <t>Chiropodist clinic</t>
+  </si>
+  <si>
     <t>554041000005106</t>
   </si>
   <si>
+    <t>Health administration</t>
+  </si>
+  <si>
     <t>554021000005101</t>
   </si>
   <si>
+    <t>Health visitors</t>
+  </si>
+  <si>
     <t>550681000005102</t>
   </si>
   <si>
+    <t>dental practice</t>
+  </si>
+  <si>
     <t>550691000005104</t>
   </si>
   <si>
+    <t>Dental care clinic</t>
+  </si>
+  <si>
     <t>550701000005104</t>
   </si>
   <si>
+    <t>Dental technician clinic</t>
+  </si>
+  <si>
     <t>554231000005106</t>
   </si>
   <si>
+    <t>Vaccination clinic</t>
+  </si>
+  <si>
     <t>554051000005108</t>
   </si>
   <si>
+    <t>Reflexology clinic</t>
+  </si>
+  <si>
     <t>550811000005108</t>
   </si>
   <si>
+    <t>Administrative unit</t>
+  </si>
+  <si>
     <t>547211000005108</t>
   </si>
   <si>
+    <t>Municipality</t>
+  </si>
+  <si>
     <t>550891000005100</t>
   </si>
   <si>
+    <t>Private</t>
+  </si>
+  <si>
     <t>550881000005103</t>
   </si>
   <si>
+    <t>Region</t>
+  </si>
+  <si>
     <t>550411000005105</t>
   </si>
   <si>
+    <t>Other health institution</t>
+  </si>
+  <si>
     <t>554851000005102</t>
   </si>
   <si>
+    <t>Asylum centre</t>
+  </si>
+  <si>
     <t>550861000005106</t>
   </si>
   <si>
+    <t>Physiotherapy and occupational clinic</t>
+  </si>
+  <si>
     <t>554881000005108</t>
   </si>
   <si>
+    <t>Handicap and psychiatry</t>
+  </si>
+  <si>
     <t>554861000005100</t>
   </si>
   <si>
+    <t>Handicap</t>
+  </si>
+  <si>
     <t>554821000005109</t>
   </si>
   <si>
+    <t>Home care</t>
+  </si>
+  <si>
     <t>554411000005101</t>
   </si>
   <si>
+    <t>Employment agency</t>
+  </si>
+  <si>
     <t>554871000005105</t>
   </si>
   <si>
+    <t>Psychiatry</t>
+  </si>
+  <si>
     <t>550821000005102</t>
   </si>
   <si>
+    <t>Service unit</t>
+  </si>
+  <si>
     <t>550871000005101</t>
   </si>
   <si>
+    <t>Emergency admission unit</t>
+  </si>
+  <si>
     <t>554241000005103</t>
   </si>
   <si>
+    <t>Technical location number</t>
+  </si>
+  <si>
     <t>550841000005107</t>
   </si>
   <si>
+    <t>Research unit</t>
+  </si>
+  <si>
     <t>550851000005109</t>
   </si>
   <si>
+    <t>Clinical unit</t>
+  </si>
+  <si>
     <t>551611000005102</t>
   </si>
   <si>
+    <t>Surgical ward</t>
+  </si>
+  <si>
     <t>554071000005100</t>
   </si>
   <si>
+    <t>Hospital pharmacy</t>
+  </si>
+  <si>
     <t>550831000005104</t>
   </si>
   <si>
+    <t>Education unit</t>
+  </si>
+  <si>
     <t>554031000005103</t>
   </si>
   <si>
+    <t>dietician clinic</t>
+  </si>
+  <si>
     <t>557511000005107</t>
   </si>
   <si>
+    <t>Acupuncture clinic</t>
+  </si>
+  <si>
     <t>557501000005109</t>
   </si>
   <si>
+    <t>Pharmacy branch</t>
+  </si>
+  <si>
     <t>557531000005103</t>
   </si>
   <si>
+    <t>Prosthetist clinic</t>
+  </si>
+  <si>
     <t>557591000005104</t>
   </si>
   <si>
+    <t>Web-based care</t>
+  </si>
+  <si>
     <t>557521000005101</t>
   </si>
   <si>
+    <t>Alternative treatment clinic</t>
+  </si>
+  <si>
     <t>557561000005105</t>
   </si>
   <si>
+    <t>Consulting firm</t>
+  </si>
+  <si>
     <t>557541000005106</t>
   </si>
   <si>
+    <t>Cosmetic treatment clinic</t>
+  </si>
+  <si>
     <t>557581000005102</t>
   </si>
   <si>
+    <t>Optometrist or optician clinic</t>
+  </si>
+  <si>
     <t>556841000005105</t>
   </si>
   <si>
+    <t>Social psychological counseling</t>
+  </si>
+  <si>
     <t>557671000005101</t>
   </si>
   <si>
+    <t>Osteopathy clinic</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
     <t>398070004</t>
   </si>
   <si>
+    <t>State</t>
+  </si>
+  <si>
     <t>394761003</t>
   </si>
   <si>
+    <t>General practitioner practice site</t>
+  </si>
+  <si>
     <t>20078004</t>
   </si>
   <si>
+    <t>Substance abuse treatment center</t>
+  </si>
+  <si>
     <t>722173008</t>
   </si>
   <si>
+    <t>Prison based care site</t>
+  </si>
+  <si>
     <t>702871004</t>
   </si>
   <si>
+    <t>Infertility clinic</t>
+  </si>
+  <si>
     <t>276037005</t>
   </si>
   <si>
+    <t>Volunteer helper</t>
+  </si>
+  <si>
     <t>22232009</t>
   </si>
   <si>
+    <t>Hospital</t>
+  </si>
+  <si>
     <t>702824005</t>
   </si>
   <si>
+    <t>Audiology clinic</t>
+  </si>
+  <si>
     <t>42665001</t>
   </si>
   <si>
+    <t>Nursing home</t>
+  </si>
+  <si>
     <t>264361005</t>
   </si>
   <si>
+    <t>Health centre</t>
+  </si>
+  <si>
     <t>703069008</t>
   </si>
   <si>
+    <t>Nurse practitioner clinic</t>
+  </si>
+  <si>
     <t>309964003</t>
   </si>
   <si>
+    <t>Radiology department</t>
+  </si>
+  <si>
     <t>309904001</t>
   </si>
   <si>
+    <t>Intensive care unit</t>
+  </si>
+  <si>
     <t>309939001</t>
   </si>
   <si>
+    <t>Palliative care department</t>
+  </si>
+  <si>
     <t>225728007</t>
   </si>
   <si>
+    <t>Accident and Emergency department</t>
+  </si>
+  <si>
     <t>255203001</t>
   </si>
   <si>
+    <t>Additional values</t>
+  </si>
+  <si>
     <t>264372000</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
+    <t>Pharmacy</t>
   </si>
 </sst>
 </file>
@@ -581,7 +786,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -600,424 +805,598 @@
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>33</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>35</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>39</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>41</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B8" s="2"/>
+        <v>42</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B9" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>45</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B10" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>47</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B11" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>49</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B12" s="2"/>
+        <v>50</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>51</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>53</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B14" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>55</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B15" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>57</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B16" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>59</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B17" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>61</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B18" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>63</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B19" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>65</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B20" s="2"/>
+        <v>66</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>67</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B21" s="2"/>
+        <v>68</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>69</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="B22" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>71</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B23" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>73</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B24" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>75</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B25" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>77</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="B26" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>79</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B27" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>81</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B28" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>83</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="B29" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>85</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="B30" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>87</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B31" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>89</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B32" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>91</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B33" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>93</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="B34" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>95</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="B35" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>97</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="B36" s="2"/>
+        <v>98</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>99</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="B37" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>101</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="B38" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>103</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="B39" s="2"/>
+        <v>104</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>105</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="B40" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>107</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="B41" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>109</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B42" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>111</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="B43" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>113</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="B44" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>115</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="B45" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>117</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="B46" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>119</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="B47" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>121</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="B48" s="2"/>
+        <v>122</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>123</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="B49" s="2"/>
+        <v>124</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>125</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="B50" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>127</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="B51" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>129</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="B52" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>131</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="B53" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>132</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="B54" s="2"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="B55" s="2"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="B56" s="2"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="B57" s="2"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="B58" s="2"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="B59" s="2"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="B60" s="2"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="B61" s="2"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="B62" s="2"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="B63" s="2"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="B64" s="2"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="B65" s="2"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="B66" s="2"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="B67" s="2"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="B68" s="2"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="B69" s="2"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>100</v>
+        <v>133</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T09:45:49+00:00</t>
+    <t>2024-05-12T11:37:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -7,8 +7,8 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from SNOWMED CT" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from SNOWMED CT 2" r:id="rId5" sheetId="3"/>
+    <sheet name="Include from SNOMED CT" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from SNOMED CT 2" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T11:37:02+00:00</t>
+    <t>2024-06-03T20:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:12:53+00:00</t>
+    <t>2024-06-25T21:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:21:07+00:00</t>
+    <t>2024-06-25T21:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:20:43+00:00</t>
+    <t>2024-06-25T21:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:42:34+00:00</t>
+    <t>2024-06-26T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T14:36:19+00:00</t>
+    <t>2024-06-27T10:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-27T10:47:07+00:00</t>
+    <t>2024-08-11T15:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from SNOMED CT" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-11T15:57:41+00:00</t>
+    <t>2024-10-17T12:12:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="169">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:12:58+00:00</t>
+    <t>2024-10-17T12:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,214 +109,418 @@
     <t>554221000005108</t>
   </si>
   <si>
+    <t>Dwilling place</t>
+  </si>
+  <si>
     <t>546821000005103</t>
   </si>
   <si>
+    <t>Occupational therapy clinic</t>
+  </si>
+  <si>
     <t>547011000005103</t>
   </si>
   <si>
+    <t>Physiotherapy clinic</t>
+  </si>
+  <si>
     <t>546811000005109</t>
   </si>
   <si>
+    <t>Rehabilitation center</t>
+  </si>
+  <si>
     <t>550621000005101</t>
   </si>
   <si>
+    <t>District nursing</t>
+  </si>
+  <si>
     <t>550631000005103</t>
   </si>
   <si>
+    <t>Midwife clinic</t>
+  </si>
+  <si>
     <t>550641000005106</t>
   </si>
   <si>
+    <t>Chiropractic clinic</t>
+  </si>
+  <si>
     <t>550651000005108</t>
   </si>
   <si>
+    <t>Medical laboratory</t>
+  </si>
+  <si>
     <t>550661000005105</t>
   </si>
   <si>
+    <t>Emergency medical service</t>
+  </si>
+  <si>
     <t>554211000005102</t>
   </si>
   <si>
+    <t>Prehospital unit</t>
+  </si>
+  <si>
     <t>550711000005101</t>
   </si>
   <si>
+    <t>Psychological counseling clinic</t>
+  </si>
+  <si>
     <t>550671000005100</t>
   </si>
   <si>
+    <t>Medical specialist practice site</t>
+  </si>
+  <si>
     <t>554061000005105</t>
   </si>
   <si>
+    <t>Chiropodist clinic</t>
+  </si>
+  <si>
     <t>554041000005106</t>
   </si>
   <si>
+    <t>Health administration</t>
+  </si>
+  <si>
     <t>554021000005101</t>
   </si>
   <si>
+    <t>Health visitors</t>
+  </si>
+  <si>
     <t>550681000005102</t>
   </si>
   <si>
+    <t>dental practice</t>
+  </si>
+  <si>
     <t>550691000005104</t>
   </si>
   <si>
+    <t>Dental care clinic</t>
+  </si>
+  <si>
     <t>550701000005104</t>
   </si>
   <si>
+    <t>Dental technician clinic</t>
+  </si>
+  <si>
     <t>554231000005106</t>
   </si>
   <si>
+    <t>Vaccination clinic</t>
+  </si>
+  <si>
     <t>554051000005108</t>
   </si>
   <si>
+    <t>Reflexology clinic</t>
+  </si>
+  <si>
     <t>550811000005108</t>
   </si>
   <si>
+    <t>Administrative unit</t>
+  </si>
+  <si>
     <t>547211000005108</t>
   </si>
   <si>
+    <t>Municipality</t>
+  </si>
+  <si>
     <t>550891000005100</t>
   </si>
   <si>
+    <t>Private</t>
+  </si>
+  <si>
     <t>550881000005103</t>
   </si>
   <si>
+    <t>Region</t>
+  </si>
+  <si>
     <t>550411000005105</t>
   </si>
   <si>
+    <t>Other health institution</t>
+  </si>
+  <si>
     <t>554851000005102</t>
   </si>
   <si>
+    <t>Asylum centre</t>
+  </si>
+  <si>
     <t>550861000005106</t>
   </si>
   <si>
+    <t>Physiotherapy and occupational clinic</t>
+  </si>
+  <si>
     <t>554881000005108</t>
   </si>
   <si>
+    <t>Handicap and psychiatry</t>
+  </si>
+  <si>
     <t>554861000005100</t>
   </si>
   <si>
+    <t>Handicap</t>
+  </si>
+  <si>
     <t>554821000005109</t>
   </si>
   <si>
+    <t>Home care</t>
+  </si>
+  <si>
     <t>554411000005101</t>
   </si>
   <si>
+    <t>Employment agency</t>
+  </si>
+  <si>
     <t>554871000005105</t>
   </si>
   <si>
+    <t>Psychiatry</t>
+  </si>
+  <si>
     <t>550821000005102</t>
   </si>
   <si>
+    <t>Service unit</t>
+  </si>
+  <si>
     <t>550871000005101</t>
   </si>
   <si>
+    <t>Emergency admission unit</t>
+  </si>
+  <si>
     <t>554241000005103</t>
   </si>
   <si>
+    <t>Technical location number</t>
+  </si>
+  <si>
     <t>550841000005107</t>
   </si>
   <si>
+    <t>Research unit</t>
+  </si>
+  <si>
     <t>550851000005109</t>
   </si>
   <si>
+    <t>Clinical unit</t>
+  </si>
+  <si>
     <t>551611000005102</t>
   </si>
   <si>
+    <t>Surgical ward</t>
+  </si>
+  <si>
     <t>554071000005100</t>
   </si>
   <si>
+    <t>Hospital pharmacy</t>
+  </si>
+  <si>
     <t>550831000005104</t>
   </si>
   <si>
+    <t>Education unit</t>
+  </si>
+  <si>
     <t>554031000005103</t>
   </si>
   <si>
+    <t>dietician clinic</t>
+  </si>
+  <si>
     <t>557511000005107</t>
   </si>
   <si>
+    <t>Acupuncture clinic</t>
+  </si>
+  <si>
     <t>557501000005109</t>
   </si>
   <si>
+    <t>Pharmacy branch</t>
+  </si>
+  <si>
     <t>557531000005103</t>
   </si>
   <si>
+    <t>Prosthetist clinic</t>
+  </si>
+  <si>
     <t>557591000005104</t>
   </si>
   <si>
+    <t>Web-based care</t>
+  </si>
+  <si>
     <t>557521000005101</t>
   </si>
   <si>
+    <t>Alternative treatment clinic</t>
+  </si>
+  <si>
     <t>557561000005105</t>
   </si>
   <si>
+    <t>Consulting firm</t>
+  </si>
+  <si>
     <t>557541000005106</t>
   </si>
   <si>
+    <t>Cosmetic treatment clinic</t>
+  </si>
+  <si>
     <t>557581000005102</t>
   </si>
   <si>
+    <t>Optometrist or optician clinic</t>
+  </si>
+  <si>
     <t>556841000005105</t>
   </si>
   <si>
+    <t>Social psychological counseling</t>
+  </si>
+  <si>
     <t>557671000005101</t>
   </si>
   <si>
+    <t>Osteopathy clinic</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
     <t>398070004</t>
   </si>
   <si>
+    <t>State</t>
+  </si>
+  <si>
     <t>394761003</t>
   </si>
   <si>
+    <t>General practitioner practice site</t>
+  </si>
+  <si>
     <t>20078004</t>
   </si>
   <si>
+    <t>Substance abuse treatment center</t>
+  </si>
+  <si>
     <t>722173008</t>
   </si>
   <si>
+    <t>Prison based care site</t>
+  </si>
+  <si>
     <t>702871004</t>
   </si>
   <si>
+    <t>Infertility clinic</t>
+  </si>
+  <si>
     <t>276037005</t>
   </si>
   <si>
+    <t>Volunteer helper</t>
+  </si>
+  <si>
     <t>22232009</t>
   </si>
   <si>
+    <t>Hospital</t>
+  </si>
+  <si>
     <t>702824005</t>
   </si>
   <si>
+    <t>Audiology clinic</t>
+  </si>
+  <si>
     <t>42665001</t>
   </si>
   <si>
+    <t>Nursing home</t>
+  </si>
+  <si>
     <t>264361005</t>
   </si>
   <si>
+    <t>Health centre</t>
+  </si>
+  <si>
     <t>703069008</t>
   </si>
   <si>
+    <t>Nurse practitioner clinic</t>
+  </si>
+  <si>
     <t>309964003</t>
   </si>
   <si>
+    <t>Radiology department</t>
+  </si>
+  <si>
     <t>309904001</t>
   </si>
   <si>
+    <t>Intensive care unit</t>
+  </si>
+  <si>
     <t>309939001</t>
   </si>
   <si>
+    <t>Palliative care department</t>
+  </si>
+  <si>
     <t>225728007</t>
   </si>
   <si>
+    <t>Accident and Emergency department</t>
+  </si>
+  <si>
     <t>255203001</t>
   </si>
   <si>
+    <t>Additional values</t>
+  </si>
+  <si>
     <t>264372000</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
+    <t>Pharmacy</t>
   </si>
 </sst>
 </file>
@@ -581,7 +786,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -600,424 +805,598 @@
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>33</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>35</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>39</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>41</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B8" s="2"/>
+        <v>42</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B9" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>45</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B10" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>47</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B11" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>49</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B12" s="2"/>
+        <v>50</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>51</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>53</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B14" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>55</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B15" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>57</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B16" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>59</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B17" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>61</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B18" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>63</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B19" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>65</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B20" s="2"/>
+        <v>66</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>67</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B21" s="2"/>
+        <v>68</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>69</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="B22" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>71</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B23" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>73</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B24" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>75</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B25" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>77</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="B26" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>79</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B27" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>81</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B28" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>83</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="B29" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>85</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="B30" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>87</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B31" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>89</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B32" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>91</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B33" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>93</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="B34" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>95</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="B35" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>97</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="B36" s="2"/>
+        <v>98</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>99</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="B37" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>101</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="B38" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>103</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="B39" s="2"/>
+        <v>104</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>105</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="B40" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>107</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="B41" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>109</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B42" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>111</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="B43" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>113</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="B44" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>115</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="B45" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>117</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="B46" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>119</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="B47" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>121</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="B48" s="2"/>
+        <v>122</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>123</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="B49" s="2"/>
+        <v>124</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>125</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="B50" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>127</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="B51" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>129</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="B52" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>131</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="B53" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>132</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="B54" s="2"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="B55" s="2"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="B56" s="2"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="B57" s="2"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="B58" s="2"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="B59" s="2"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="B60" s="2"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="B61" s="2"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="B62" s="2"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="B63" s="2"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="B64" s="2"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="B65" s="2"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="B66" s="2"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="B67" s="2"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="B68" s="2"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="B69" s="2"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>100</v>
+        <v>133</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T06:07:37+00:00</t>
+    <t>2024-10-27T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T12:31:37+00:00</t>
+    <t>2024-11-04T14:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:15:57+00:00</t>
+    <t>2024-11-04T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:58:42+00:00</t>
+    <t>2024-11-04T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:07:28+00:00</t>
+    <t>2024-11-05T12:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="169">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.4.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T12:45:46+00:00</t>
+    <t>2024-11-15T12:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,214 +109,418 @@
     <t>554221000005108</t>
   </si>
   <si>
+    <t>Dwilling place</t>
+  </si>
+  <si>
     <t>546821000005103</t>
   </si>
   <si>
+    <t>Occupational therapy clinic</t>
+  </si>
+  <si>
     <t>547011000005103</t>
   </si>
   <si>
+    <t>Physiotherapy clinic</t>
+  </si>
+  <si>
     <t>546811000005109</t>
   </si>
   <si>
+    <t>Rehabilitation center</t>
+  </si>
+  <si>
     <t>550621000005101</t>
   </si>
   <si>
+    <t>District nursing</t>
+  </si>
+  <si>
     <t>550631000005103</t>
   </si>
   <si>
+    <t>Midwife clinic</t>
+  </si>
+  <si>
     <t>550641000005106</t>
   </si>
   <si>
+    <t>Chiropractic clinic</t>
+  </si>
+  <si>
     <t>550651000005108</t>
   </si>
   <si>
+    <t>Medical laboratory</t>
+  </si>
+  <si>
     <t>550661000005105</t>
   </si>
   <si>
+    <t>Emergency medical service</t>
+  </si>
+  <si>
     <t>554211000005102</t>
   </si>
   <si>
+    <t>Prehospital unit</t>
+  </si>
+  <si>
     <t>550711000005101</t>
   </si>
   <si>
+    <t>Psychological counseling clinic</t>
+  </si>
+  <si>
     <t>550671000005100</t>
   </si>
   <si>
+    <t>Medical specialist practice site</t>
+  </si>
+  <si>
     <t>554061000005105</t>
   </si>
   <si>
+    <t>Chiropodist clinic</t>
+  </si>
+  <si>
     <t>554041000005106</t>
   </si>
   <si>
+    <t>Health administration</t>
+  </si>
+  <si>
     <t>554021000005101</t>
   </si>
   <si>
+    <t>Health visitors</t>
+  </si>
+  <si>
     <t>550681000005102</t>
   </si>
   <si>
+    <t>dental practice</t>
+  </si>
+  <si>
     <t>550691000005104</t>
   </si>
   <si>
+    <t>Dental care clinic</t>
+  </si>
+  <si>
     <t>550701000005104</t>
   </si>
   <si>
+    <t>Dental technician clinic</t>
+  </si>
+  <si>
     <t>554231000005106</t>
   </si>
   <si>
+    <t>Vaccination clinic</t>
+  </si>
+  <si>
     <t>554051000005108</t>
   </si>
   <si>
+    <t>Reflexology clinic</t>
+  </si>
+  <si>
     <t>550811000005108</t>
   </si>
   <si>
+    <t>Administrative unit</t>
+  </si>
+  <si>
     <t>547211000005108</t>
   </si>
   <si>
+    <t>Municipality</t>
+  </si>
+  <si>
     <t>550891000005100</t>
   </si>
   <si>
+    <t>Private</t>
+  </si>
+  <si>
     <t>550881000005103</t>
   </si>
   <si>
+    <t>Region</t>
+  </si>
+  <si>
     <t>550411000005105</t>
   </si>
   <si>
+    <t>Other health institution</t>
+  </si>
+  <si>
     <t>554851000005102</t>
   </si>
   <si>
+    <t>Asylum centre</t>
+  </si>
+  <si>
     <t>550861000005106</t>
   </si>
   <si>
+    <t>Physiotherapy and occupational clinic</t>
+  </si>
+  <si>
     <t>554881000005108</t>
   </si>
   <si>
+    <t>Handicap and psychiatry</t>
+  </si>
+  <si>
     <t>554861000005100</t>
   </si>
   <si>
+    <t>Handicap</t>
+  </si>
+  <si>
     <t>554821000005109</t>
   </si>
   <si>
+    <t>Home care</t>
+  </si>
+  <si>
     <t>554411000005101</t>
   </si>
   <si>
+    <t>Employment agency</t>
+  </si>
+  <si>
     <t>554871000005105</t>
   </si>
   <si>
+    <t>Psychiatry</t>
+  </si>
+  <si>
     <t>550821000005102</t>
   </si>
   <si>
+    <t>Service unit</t>
+  </si>
+  <si>
     <t>550871000005101</t>
   </si>
   <si>
+    <t>Emergency admission unit</t>
+  </si>
+  <si>
     <t>554241000005103</t>
   </si>
   <si>
+    <t>Technical location number</t>
+  </si>
+  <si>
     <t>550841000005107</t>
   </si>
   <si>
+    <t>Research unit</t>
+  </si>
+  <si>
     <t>550851000005109</t>
   </si>
   <si>
+    <t>Clinical unit</t>
+  </si>
+  <si>
     <t>551611000005102</t>
   </si>
   <si>
+    <t>Surgical ward</t>
+  </si>
+  <si>
     <t>554071000005100</t>
   </si>
   <si>
+    <t>Hospital pharmacy</t>
+  </si>
+  <si>
     <t>550831000005104</t>
   </si>
   <si>
+    <t>Education unit</t>
+  </si>
+  <si>
     <t>554031000005103</t>
   </si>
   <si>
+    <t>dietician clinic</t>
+  </si>
+  <si>
     <t>557511000005107</t>
   </si>
   <si>
+    <t>Acupuncture clinic</t>
+  </si>
+  <si>
     <t>557501000005109</t>
   </si>
   <si>
+    <t>Pharmacy branch</t>
+  </si>
+  <si>
     <t>557531000005103</t>
   </si>
   <si>
+    <t>Prosthetist clinic</t>
+  </si>
+  <si>
     <t>557591000005104</t>
   </si>
   <si>
+    <t>Web-based care</t>
+  </si>
+  <si>
     <t>557521000005101</t>
   </si>
   <si>
+    <t>Alternative treatment clinic</t>
+  </si>
+  <si>
     <t>557561000005105</t>
   </si>
   <si>
+    <t>Consulting firm</t>
+  </si>
+  <si>
     <t>557541000005106</t>
   </si>
   <si>
+    <t>Cosmetic treatment clinic</t>
+  </si>
+  <si>
     <t>557581000005102</t>
   </si>
   <si>
+    <t>Optometrist or optician clinic</t>
+  </si>
+  <si>
     <t>556841000005105</t>
   </si>
   <si>
+    <t>Social psychological counseling</t>
+  </si>
+  <si>
     <t>557671000005101</t>
   </si>
   <si>
+    <t>Osteopathy clinic</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
     <t>398070004</t>
   </si>
   <si>
+    <t>State</t>
+  </si>
+  <si>
     <t>394761003</t>
   </si>
   <si>
+    <t>General practitioner practice site</t>
+  </si>
+  <si>
     <t>20078004</t>
   </si>
   <si>
+    <t>Substance abuse treatment center</t>
+  </si>
+  <si>
     <t>722173008</t>
   </si>
   <si>
+    <t>Prison based care site</t>
+  </si>
+  <si>
     <t>702871004</t>
   </si>
   <si>
+    <t>Infertility clinic</t>
+  </si>
+  <si>
     <t>276037005</t>
   </si>
   <si>
+    <t>Volunteer helper</t>
+  </si>
+  <si>
     <t>22232009</t>
   </si>
   <si>
+    <t>Hospital</t>
+  </si>
+  <si>
     <t>702824005</t>
   </si>
   <si>
+    <t>Audiology clinic</t>
+  </si>
+  <si>
     <t>42665001</t>
   </si>
   <si>
+    <t>Nursing home</t>
+  </si>
+  <si>
     <t>264361005</t>
   </si>
   <si>
+    <t>Health centre</t>
+  </si>
+  <si>
     <t>703069008</t>
   </si>
   <si>
+    <t>Nurse practitioner clinic</t>
+  </si>
+  <si>
     <t>309964003</t>
   </si>
   <si>
+    <t>Radiology department</t>
+  </si>
+  <si>
     <t>309904001</t>
   </si>
   <si>
+    <t>Intensive care unit</t>
+  </si>
+  <si>
     <t>309939001</t>
   </si>
   <si>
+    <t>Palliative care department</t>
+  </si>
+  <si>
     <t>225728007</t>
   </si>
   <si>
+    <t>Accident and Emergency department</t>
+  </si>
+  <si>
     <t>255203001</t>
   </si>
   <si>
+    <t>Additional values</t>
+  </si>
+  <si>
     <t>264372000</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
+    <t>Pharmacy</t>
   </si>
 </sst>
 </file>
@@ -581,7 +786,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -600,424 +805,598 @@
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>33</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>35</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>39</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>41</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B8" s="2"/>
+        <v>42</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B9" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>45</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B10" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>47</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B11" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>49</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B12" s="2"/>
+        <v>50</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>51</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>53</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B14" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>55</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B15" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>57</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B16" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>59</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B17" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>61</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B18" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>63</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B19" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>65</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B20" s="2"/>
+        <v>66</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>67</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B21" s="2"/>
+        <v>68</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>69</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="B22" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>71</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B23" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>73</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B24" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>75</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B25" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>77</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="B26" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>79</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B27" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>81</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B28" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>83</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="B29" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>85</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="B30" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>87</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B31" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>89</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B32" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>91</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B33" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>93</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="B34" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>95</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="B35" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>97</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="B36" s="2"/>
+        <v>98</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>99</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="B37" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>101</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="B38" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>103</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="B39" s="2"/>
+        <v>104</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>105</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="B40" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>107</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="B41" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>109</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B42" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>111</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="B43" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>113</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="B44" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>115</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="B45" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>117</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="B46" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>119</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="B47" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>121</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="B48" s="2"/>
+        <v>122</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>123</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="B49" s="2"/>
+        <v>124</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>125</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="B50" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>127</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="B51" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>129</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="B52" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>131</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="B53" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>132</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="B54" s="2"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="B55" s="2"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="B56" s="2"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="B57" s="2"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="B58" s="2"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="B59" s="2"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="B60" s="2"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="B61" s="2"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="B62" s="2"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="B63" s="2"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="B64" s="2"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="B65" s="2"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="B66" s="2"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="B67" s="2"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="B68" s="2"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="B69" s="2"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>100</v>
+        <v>133</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T12:49:28+00:00</t>
+    <t>2024-11-15T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T13:03:47+00:00</t>
+    <t>2024-11-29T07:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T07:41:39+00:00</t>
+    <t>2024-11-29T10:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T10:20:07+00:00</t>
+    <t>2024-12-11T08:38:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T08:38:49+00:00</t>
+    <t>2024-12-11T09:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T09:50:58+00:00</t>
+    <t>2024-12-16T15:09:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:09:03+00:00</t>
+    <t>2024-12-16T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sor-organization-type.xlsx
+++ b/ValueSet-sor-organization-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:16:17+00:00</t>
+    <t>2024-12-16T15:31:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
